--- a/experiments/results/densenet101/CIFAR-10/baseline/energy/adaptive/avg/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-10/baseline/energy/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -764,6 +764,55 @@
       <c r="O8" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.05,type=avg</t>
         </is>
       </c>
     </row>
